--- a/ig/improve-doc/ValueSet-JDV-J148-ReferenceRangeAppliesTo-CISIS.xlsx
+++ b/ig/improve-doc/ValueSet-JDV-J148-ReferenceRangeAppliesTo-CISIS.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20230331120000</t>
+    <t>20240927120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-31T12:00:00+01:00</t>
+    <t>2024-09-27T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
